--- a/연구코드/aec/results/강남/multivariable_results.xlsx
+++ b/연구코드/aec/results/강남/multivariable_results.xlsx
@@ -715,10 +715,10 @@
         <v>0.624</v>
       </c>
       <c r="C14" t="n">
-        <v>0.72</v>
+        <v>0.7196</v>
       </c>
       <c r="D14" t="n">
-        <v>0.7522</v>
+        <v>0.7518</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -733,13 +733,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.5937</v>
+        <v>0.5924</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6922</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7262</v>
+        <v>0.7268</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -754,13 +754,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6544</v>
+        <v>0.6554</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7451</v>
+        <v>0.7453</v>
       </c>
       <c r="D16" t="n">
-        <v>0.777</v>
+        <v>0.7778</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>217473871818.365</v>
+        <v>217473878827.7454</v>
       </c>
       <c r="F10" t="n">
         <v>15.7361</v>
@@ -2351,7 +2351,7 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>1.699137147922753e+31</v>
+        <v>1.699137376042557e+31</v>
       </c>
       <c r="F12" t="n">
         <v>40.6982</v>
@@ -2381,7 +2381,7 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>115308986.9962</v>
+        <v>115308987.6496</v>
       </c>
       <c r="F13" t="n">
         <v>9.762</v>
@@ -2471,7 +2471,7 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>5.482749553451126e+17</v>
+        <v>5.482749880061208e+17</v>
       </c>
       <c r="F16" t="n">
         <v>23.89</v>
@@ -2501,7 +2501,7 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>1.304604097987171e+49</v>
+        <v>1.30460441715463e+49</v>
       </c>
       <c r="F17" t="n">
         <v>62.3713</v>
@@ -2531,7 +2531,7 @@
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>1.95718576571727e+163</v>
+        <v>1.95718771375254e+163</v>
       </c>
       <c r="F18" t="n">
         <v>197.9569</v>
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>9.083629393035032e+51</v>
+        <v>9.083631727057405e+51</v>
       </c>
       <c r="F23" t="n">
         <v>65.79649999999999</v>
@@ -2707,7 +2707,7 @@
         <v>15.0399</v>
       </c>
       <c r="C24" t="n">
-        <v>3402110.5322</v>
+        <v>3402110.5545</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
@@ -2769,7 +2769,7 @@
         <v>11.6828</v>
       </c>
       <c r="C26" t="n">
-        <v>118513.8274</v>
+        <v>118513.828</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
@@ -2989,7 +2989,7 @@
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>8.090970313194803e+45</v>
+        <v>8.090972069683324e+45</v>
       </c>
       <c r="F33" t="n">
         <v>58.4414</v>
@@ -3019,7 +3019,7 @@
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>4.168247429080646e+40</v>
+        <v>4.168248213930226e+40</v>
       </c>
       <c r="F34" t="n">
         <v>52.1026</v>
@@ -3049,7 +3049,7 @@
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>1.968356071724979e+19</v>
+        <v>1.968356210021403e+19</v>
       </c>
       <c r="F35" t="n">
         <v>25.9442</v>
@@ -3079,7 +3079,7 @@
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>9.852496779102026e+50</v>
+        <v>9.852499195344899e+50</v>
       </c>
       <c r="F36" t="n">
         <v>64.55549999999999</v>
@@ -3133,7 +3133,7 @@
         <v>23.8806</v>
       </c>
       <c r="C38" t="n">
-        <v>23506857561.9763</v>
+        <v>23506857810.2528</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
@@ -3144,7 +3144,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>33203.1824</v>
+        <v>33203.1864</v>
       </c>
       <c r="G38" t="n">
         <v>0.0007</v>
@@ -3358,7 +3358,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7522</v>
+        <v>0.7518</v>
       </c>
     </row>
     <row r="5">
@@ -3368,7 +3368,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7262</v>
+        <v>0.7268</v>
       </c>
     </row>
     <row r="6">
@@ -3378,7 +3378,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.777</v>
+        <v>0.7778</v>
       </c>
     </row>
     <row r="7">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5937</v>
+        <v>0.5924</v>
       </c>
     </row>
     <row r="6">
@@ -3934,7 +3934,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6544</v>
+        <v>0.6554</v>
       </c>
     </row>
     <row r="7">
@@ -4755,7 +4755,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.72</v>
+        <v>0.7196</v>
       </c>
     </row>
     <row r="5">
@@ -4765,7 +4765,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6922</v>
+        <v>0.6929999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7451</v>
+        <v>0.7453</v>
       </c>
     </row>
     <row r="7">

--- a/연구코드/aec/results/강남/multivariable_results.xlsx
+++ b/연구코드/aec/results/강남/multivariable_results.xlsx
@@ -519,16 +519,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1938</v>
+        <v>0.1909</v>
       </c>
       <c r="C4" t="n">
         <v>0.5507</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6358</v>
+        <v>0.6356000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6599</v>
+        <v>0.6597</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -543,7 +543,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1914</v>
+        <v>0.1889</v>
       </c>
       <c r="C5" t="n">
         <v>0.5502</v>
@@ -568,7 +568,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.6316e-75</t>
+          <t>3.1021e-75</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -599,16 +599,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>27.3719</v>
+        <v>27.4216</v>
       </c>
       <c r="C7" t="n">
         <v>20.4337</v>
       </c>
       <c r="D7" t="n">
-        <v>18.3967</v>
+        <v>18.4019</v>
       </c>
       <c r="E7" t="n">
-        <v>17.7773</v>
+        <v>17.784</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -623,16 +623,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>21.5901</v>
+        <v>21.6665</v>
       </c>
       <c r="C8" t="n">
         <v>15.0485</v>
       </c>
       <c r="D8" t="n">
-        <v>13.5588</v>
+        <v>13.5726</v>
       </c>
       <c r="E8" t="n">
-        <v>13.1377</v>
+        <v>13.1539</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -647,16 +647,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15833.41</v>
+        <v>15837.48</v>
       </c>
       <c r="C9" t="n">
         <v>14849.28</v>
       </c>
       <c r="D9" t="n">
-        <v>14507.89</v>
+        <v>14506.83</v>
       </c>
       <c r="E9" t="n">
-        <v>14455.29</v>
+        <v>14454.56</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -671,16 +671,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>15865.94</v>
+        <v>15864.59</v>
       </c>
       <c r="C10" t="n">
         <v>14865.54</v>
       </c>
       <c r="D10" t="n">
-        <v>14551.27</v>
+        <v>14544.79</v>
       </c>
       <c r="E10" t="n">
-        <v>14666.77</v>
+        <v>14660.61</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -761,10 +761,10 @@
         <v>0.624</v>
       </c>
       <c r="D14" t="n">
-        <v>0.7196</v>
+        <v>0.7191</v>
       </c>
       <c r="E14" t="n">
-        <v>0.7548</v>
+        <v>0.7542</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -779,16 +779,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6512</v>
+        <v>0.651</v>
       </c>
       <c r="C15" t="n">
         <v>0.5924</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.6931</v>
       </c>
       <c r="E15" t="n">
-        <v>0.7297</v>
+        <v>0.7289</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -803,16 +803,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7065</v>
+        <v>0.7064</v>
       </c>
       <c r="C16" t="n">
         <v>0.6554</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7453</v>
+        <v>0.7447</v>
       </c>
       <c r="E16" t="n">
-        <v>0.7806</v>
+        <v>0.78</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>4.9233e-02</t>
+          <t>1.3192e-01</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -838,12 +838,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.1625e-01</t>
+          <t>3.8738e-01</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>4.9435e-01</t>
+          <t>7.2822e-01</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>보정 불량</t>
+          <t>보정 양호</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -887,16 +887,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.0979</v>
+        <v>0.09760000000000001</v>
       </c>
       <c r="C19" t="n">
         <v>0.0516</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1596</v>
+        <v>0.1587</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2169</v>
+        <v>0.2159</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -917,10 +917,10 @@
         <v>0.1746</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1625</v>
+        <v>0.1626</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1553</v>
+        <v>0.1554</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -935,16 +935,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1739.35</v>
+        <v>1737.82</v>
       </c>
       <c r="C21" t="n">
         <v>1787.8</v>
       </c>
       <c r="D21" t="n">
-        <v>1668.07</v>
+        <v>1667.18</v>
       </c>
       <c r="E21" t="n">
-        <v>1656.88</v>
+        <v>1656.25</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -959,16 +959,16 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1771.88</v>
+        <v>1764.93</v>
       </c>
       <c r="C22" t="n">
         <v>1804.07</v>
       </c>
       <c r="D22" t="n">
-        <v>1711.45</v>
+        <v>1705.14</v>
       </c>
       <c r="E22" t="n">
-        <v>1868.35</v>
+        <v>1862.3</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1034,19 +1034,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>105.2116</v>
+        <v>105.1799</v>
       </c>
       <c r="C2" t="n">
-        <v>104.0132</v>
+        <v>103.9832</v>
       </c>
       <c r="D2" t="n">
-        <v>106.41</v>
+        <v>106.3765</v>
       </c>
       <c r="E2" t="n">
-        <v>0.611</v>
+        <v>0.6101</v>
       </c>
       <c r="F2" t="n">
-        <v>172.192</v>
+        <v>172.3916</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -1061,23 +1061,23 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>43.5203</v>
+        <v>43.6001</v>
       </c>
       <c r="C3" t="n">
-        <v>41.4853</v>
+        <v>41.5717</v>
       </c>
       <c r="D3" t="n">
-        <v>45.5552</v>
+        <v>45.6286</v>
       </c>
       <c r="E3" t="n">
-        <v>1.0375</v>
+        <v>1.0342</v>
       </c>
       <c r="F3" t="n">
-        <v>41.9471</v>
+        <v>42.1583</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>5.0607e-263</t>
+          <t>6.1262e-265</t>
         </is>
       </c>
     </row>
@@ -1088,50 +1088,50 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-6.6477</v>
+        <v>-6.6266</v>
       </c>
       <c r="C4" t="n">
-        <v>-7.5956</v>
+        <v>-7.5735</v>
       </c>
       <c r="D4" t="n">
-        <v>-5.6997</v>
+        <v>-5.6796</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4833</v>
+        <v>0.4828</v>
       </c>
       <c r="F4" t="n">
-        <v>-13.7552</v>
+        <v>-13.7257</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>7.4249e-41</t>
+          <t>1.0666e-40</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>p25_z</t>
+          <t>mean_z</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.7075</v>
+        <v>8.114699999999999</v>
       </c>
       <c r="C5" t="n">
-        <v>-3.8052</v>
+        <v>7.0215</v>
       </c>
       <c r="D5" t="n">
-        <v>11.2202</v>
+        <v>9.2079</v>
       </c>
       <c r="E5" t="n">
-        <v>3.8303</v>
+        <v>0.5574</v>
       </c>
       <c r="F5" t="n">
-        <v>0.968</v>
+        <v>14.5591</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3.3321e-01</t>
+          <t>2.7272e-45</t>
         </is>
       </c>
     </row>
@@ -1142,23 +1142,23 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-1.4284</v>
+        <v>-2.0436</v>
       </c>
       <c r="C6" t="n">
-        <v>-3.0985</v>
+        <v>-3.1549</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2418</v>
+        <v>-0.9323</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8515</v>
+        <v>0.5666</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.6774</v>
+        <v>-3.6069</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>9.3647e-02</t>
+          <t>3.1903e-04</t>
         </is>
       </c>
     </row>
@@ -1169,23 +1169,23 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.9191</v>
+        <v>-1.324</v>
       </c>
       <c r="C7" t="n">
-        <v>-2.275</v>
+        <v>-2.4035</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4367</v>
+        <v>-0.2444</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6913</v>
+        <v>0.5504</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.3296</v>
+        <v>-2.4055</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1.8382e-01</t>
+          <t>1.6260e-02</t>
         </is>
       </c>
     </row>
@@ -1196,50 +1196,23 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-4.9021</v>
+        <v>-4.9749</v>
       </c>
       <c r="C8" t="n">
-        <v>-5.9653</v>
+        <v>-6.0277</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.839</v>
+        <v>-3.922</v>
       </c>
       <c r="E8" t="n">
-        <v>0.542</v>
+        <v>0.5368000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>-9.043900000000001</v>
+        <v>-9.2677</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>4.0938e-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>mean_z</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>4.8279</v>
-      </c>
-      <c r="C9" t="n">
-        <v>-1.9213</v>
-      </c>
-      <c r="D9" t="n">
-        <v>11.5772</v>
-      </c>
-      <c r="E9" t="n">
-        <v>3.441</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1.403</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>1.6079e-01</t>
+          <t>5.6870e-20</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1227,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1306,26 +1279,26 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-1.3782</v>
+        <v>-1.3702</v>
       </c>
       <c r="C2" t="n">
-        <v>0.252</v>
+        <v>0.2541</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2126</v>
+        <v>0.2145</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2988</v>
+        <v>0.3009</v>
       </c>
       <c r="F2" t="n">
-        <v>0.08690000000000001</v>
+        <v>0.0863</v>
       </c>
       <c r="G2" t="n">
-        <v>-15.8637</v>
+        <v>-15.8682</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1.1300e-56</t>
+          <t>1.0520e-56</t>
         </is>
       </c>
     </row>
@@ -1336,26 +1309,26 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0762</v>
+        <v>0.062</v>
       </c>
       <c r="C3" t="n">
-        <v>1.0792</v>
+        <v>1.064</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8208</v>
+        <v>0.8105</v>
       </c>
       <c r="E3" t="n">
-        <v>1.419</v>
+        <v>1.3968</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1396</v>
+        <v>0.1388</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5459000000000001</v>
+        <v>0.4466</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>5.8513e-01</t>
+          <t>6.5515e-01</t>
         </is>
       </c>
     </row>
@@ -1366,56 +1339,56 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5848</v>
+        <v>0.5831</v>
       </c>
       <c r="C4" t="n">
-        <v>1.7946</v>
+        <v>1.7916</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5624</v>
+        <v>1.5594</v>
       </c>
       <c r="E4" t="n">
-        <v>2.0613</v>
+        <v>2.0583</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0707</v>
+        <v>0.0708</v>
       </c>
       <c r="G4" t="n">
-        <v>8.271000000000001</v>
+        <v>8.2349</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.3288e-16</t>
+          <t>1.7968e-16</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>p25_z</t>
+          <t>mean_z</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.5704</v>
+        <v>-0.7599</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5653</v>
+        <v>0.4677</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1958</v>
+        <v>0.3976</v>
       </c>
       <c r="E5" t="n">
-        <v>1.632</v>
+        <v>0.5502</v>
       </c>
       <c r="F5" t="n">
-        <v>0.541</v>
+        <v>0.0829</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.0545</v>
+        <v>-9.1685</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2.9165e-01</t>
+          <t>4.7950e-20</t>
         </is>
       </c>
     </row>
@@ -1426,26 +1399,26 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0013</v>
+        <v>0.0931</v>
       </c>
       <c r="C6" t="n">
-        <v>1.0013</v>
+        <v>1.0976</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7991</v>
+        <v>0.9479</v>
       </c>
       <c r="E6" t="n">
-        <v>1.2545</v>
+        <v>1.2709</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1151</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0109</v>
+        <v>1.2444</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>9.9132e-01</t>
+          <t>2.1336e-01</t>
         </is>
       </c>
     </row>
@@ -1456,26 +1429,26 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0333</v>
+        <v>0.0906</v>
       </c>
       <c r="C7" t="n">
-        <v>1.0338</v>
+        <v>1.0948</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8606</v>
+        <v>0.9431</v>
       </c>
       <c r="E7" t="n">
-        <v>1.2419</v>
+        <v>1.271</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0936</v>
+        <v>0.0761</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3557</v>
+        <v>1.1902</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>7.2206e-01</t>
+          <t>2.3397e-01</t>
         </is>
       </c>
     </row>
@@ -1486,56 +1459,26 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3193</v>
+        <v>0.3263</v>
       </c>
       <c r="C8" t="n">
-        <v>1.3762</v>
+        <v>1.3858</v>
       </c>
       <c r="D8" t="n">
-        <v>1.1923</v>
+        <v>1.2023</v>
       </c>
       <c r="E8" t="n">
-        <v>1.5884</v>
+        <v>1.5974</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0732</v>
+        <v>0.0725</v>
       </c>
       <c r="G8" t="n">
-        <v>4.3642</v>
+        <v>4.5013</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.2758e-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>mean_z</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>-0.2588</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.772</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.3005</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1.9829</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.4813</v>
-      </c>
-      <c r="G9" t="n">
-        <v>-0.5377</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>5.9077e-01</t>
+          <t>6.7542e-06</t>
         </is>
       </c>
     </row>
@@ -1582,7 +1525,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6358</v>
+        <v>0.6356000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -1602,7 +1545,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>415.2786</v>
+        <v>484.3538</v>
       </c>
     </row>
     <row r="6">
@@ -1624,7 +1567,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18.3967</v>
+        <v>18.4019</v>
       </c>
     </row>
     <row r="8">
@@ -1634,7 +1577,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13.5588</v>
+        <v>13.5726</v>
       </c>
     </row>
     <row r="9">
@@ -1644,7 +1587,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14507.89</v>
+        <v>14506.83</v>
       </c>
     </row>
     <row r="10">
@@ -1654,7 +1597,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14551.27</v>
+        <v>14544.79</v>
       </c>
     </row>
   </sheetData>
@@ -1710,7 +1653,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7196</v>
+        <v>0.7191</v>
       </c>
     </row>
     <row r="5">
@@ -1720,7 +1663,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.6931</v>
       </c>
     </row>
     <row r="6">
@@ -1730,7 +1673,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7453</v>
+        <v>0.7447</v>
       </c>
     </row>
     <row r="7">
@@ -1740,7 +1683,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.4314</v>
+        <v>8.4872</v>
       </c>
     </row>
     <row r="8">
@@ -1751,7 +1694,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>8.1625e-01</t>
+          <t>3.8738e-01</t>
         </is>
       </c>
     </row>
@@ -1774,7 +1717,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1596</v>
+        <v>0.1587</v>
       </c>
     </row>
     <row r="11">
@@ -1784,7 +1727,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1625</v>
+        <v>0.1626</v>
       </c>
     </row>
     <row r="12">
@@ -1794,7 +1737,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1668.07</v>
+        <v>1667.18</v>
       </c>
     </row>
     <row r="13">
@@ -1804,7 +1747,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1711.45</v>
+        <v>1705.14</v>
       </c>
     </row>
     <row r="14">
@@ -1828,7 +1771,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1875,23 +1818,23 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>104.103</v>
+        <v>104.1709</v>
       </c>
       <c r="C2" t="n">
-        <v>89.14579999999999</v>
+        <v>89.2131</v>
       </c>
       <c r="D2" t="n">
-        <v>119.0602</v>
+        <v>119.1288</v>
       </c>
       <c r="E2" t="n">
-        <v>7.6257</v>
+        <v>7.626</v>
       </c>
       <c r="F2" t="n">
-        <v>13.6515</v>
+        <v>13.6599</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2.9200e-40</t>
+          <t>2.6267e-40</t>
         </is>
       </c>
     </row>
@@ -1902,23 +1845,23 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>42.2812</v>
+        <v>42.4103</v>
       </c>
       <c r="C3" t="n">
-        <v>40.2039</v>
+        <v>40.3454</v>
       </c>
       <c r="D3" t="n">
-        <v>44.3586</v>
+        <v>44.4753</v>
       </c>
       <c r="E3" t="n">
-        <v>1.0591</v>
+        <v>1.0528</v>
       </c>
       <c r="F3" t="n">
-        <v>39.922</v>
+        <v>40.2837</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>7.9896e-244</t>
+          <t>4.8290e-247</t>
         </is>
       </c>
     </row>
@@ -1929,50 +1872,50 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-6.6178</v>
+        <v>-6.5974</v>
       </c>
       <c r="C4" t="n">
-        <v>-7.5658</v>
+        <v>-7.5447</v>
       </c>
       <c r="D4" t="n">
-        <v>-5.6698</v>
+        <v>-5.65</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4833</v>
+        <v>0.483</v>
       </c>
       <c r="F4" t="n">
-        <v>-13.6924</v>
+        <v>-13.6591</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1.7634e-40</t>
+          <t>2.6539e-40</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>p25_z</t>
+          <t>mean_z</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.2529</v>
+        <v>9.4657</v>
       </c>
       <c r="C5" t="n">
-        <v>-3.2484</v>
+        <v>8.278600000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>11.7542</v>
+        <v>10.6528</v>
       </c>
       <c r="E5" t="n">
-        <v>3.8244</v>
+        <v>0.6052</v>
       </c>
       <c r="F5" t="n">
-        <v>1.112</v>
+        <v>15.6398</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2.6629e-01</t>
+          <t>1.7298e-51</t>
         </is>
       </c>
     </row>
@@ -1983,23 +1926,23 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.6967</v>
+        <v>-1.3934</v>
       </c>
       <c r="C6" t="n">
-        <v>-2.4054</v>
+        <v>-2.5807</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0121</v>
+        <v>-0.2061</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8712</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.7997</v>
+        <v>-2.3019</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>4.2403e-01</t>
+          <t>2.1465e-02</t>
         </is>
       </c>
     </row>
@@ -2010,23 +1953,23 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-1.5255</v>
+        <v>-1.9764</v>
       </c>
       <c r="C7" t="n">
-        <v>-2.8806</v>
+        <v>-3.0737</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1705</v>
+        <v>-0.879</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6909</v>
+        <v>0.5595</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.2081</v>
+        <v>-3.5326</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2.7373e-02</t>
+          <t>4.2285e-04</t>
         </is>
       </c>
     </row>
@@ -2037,887 +1980,860 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-4.7816</v>
+        <v>-4.9161</v>
       </c>
       <c r="C8" t="n">
-        <v>-6.203</v>
+        <v>-6.3177</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.3601</v>
+        <v>-3.5144</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7247</v>
+        <v>0.7146</v>
       </c>
       <c r="F8" t="n">
-        <v>-6.5979</v>
+        <v>-6.8794</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>5.6176e-11</t>
+          <t>8.5285e-12</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>mean_z</t>
+          <t>kvp_z</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.7001</v>
+        <v>1.8254</v>
       </c>
       <c r="C9" t="n">
-        <v>-1.047</v>
+        <v>0.6605</v>
       </c>
       <c r="D9" t="n">
-        <v>12.4471</v>
+        <v>2.9904</v>
       </c>
       <c r="E9" t="n">
-        <v>3.4399</v>
+        <v>0.5939</v>
       </c>
       <c r="F9" t="n">
-        <v>1.6571</v>
+        <v>3.0735</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>9.7701e-02</t>
+          <t>2.1509e-03</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>kvp_z</t>
+          <t>Model_Aquilion ONE</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.8419</v>
+        <v>5.9621</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6767</v>
+        <v>-32.5187</v>
       </c>
       <c r="D10" t="n">
-        <v>3.0072</v>
+        <v>44.443</v>
       </c>
       <c r="E10" t="n">
-        <v>0.5941</v>
+        <v>19.6189</v>
       </c>
       <c r="F10" t="n">
-        <v>3.1005</v>
+        <v>0.3039</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1.9649e-03</t>
+          <t>7.6125e-01</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Model_Aquilion ONE</t>
+          <t>Model_Aquilion PRIME</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6.831</v>
+        <v>13.0881</v>
       </c>
       <c r="C11" t="n">
-        <v>-31.6776</v>
+        <v>-8.2989</v>
       </c>
       <c r="D11" t="n">
-        <v>45.3396</v>
+        <v>34.4751</v>
       </c>
       <c r="E11" t="n">
-        <v>19.6331</v>
+        <v>10.9039</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3479</v>
+        <v>1.2003</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>7.2794e-01</t>
+          <t>2.3019e-01</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Model_Aquilion PRIME</t>
+          <t>Model_BrightSpeed</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13.2057</v>
+        <v>21.246</v>
       </c>
       <c r="C12" t="n">
-        <v>-8.1808</v>
+        <v>-16.9048</v>
       </c>
       <c r="D12" t="n">
-        <v>34.5922</v>
+        <v>59.3967</v>
       </c>
       <c r="E12" t="n">
-        <v>10.9036</v>
+        <v>19.4506</v>
       </c>
       <c r="F12" t="n">
-        <v>1.2111</v>
+        <v>1.0923</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2.2602e-01</t>
+          <t>2.7486e-01</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Model_BrightSpeed</t>
+          <t>Model_BrightSpeed S</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>20.7548</v>
+        <v>-15.3198</v>
       </c>
       <c r="C13" t="n">
-        <v>-17.4031</v>
+        <v>-53.8493</v>
       </c>
       <c r="D13" t="n">
-        <v>58.9126</v>
+        <v>23.2096</v>
       </c>
       <c r="E13" t="n">
-        <v>19.4542</v>
+        <v>19.6437</v>
       </c>
       <c r="F13" t="n">
-        <v>1.0669</v>
+        <v>-0.7799</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2.8620e-01</t>
+          <t>4.3557e-01</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Model_BrightSpeed S</t>
+          <t>Model_Brilliance 64</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-14.3311</v>
+        <v>-17.9978</v>
       </c>
       <c r="C14" t="n">
-        <v>-52.8972</v>
+        <v>-38.4401</v>
       </c>
       <c r="D14" t="n">
-        <v>24.2351</v>
+        <v>2.4445</v>
       </c>
       <c r="E14" t="n">
-        <v>19.6624</v>
+        <v>10.4222</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.7289</v>
+        <v>-1.7269</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>4.6619e-01</t>
+          <t>8.4381e-02</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Model_Brilliance 64</t>
+          <t>Model_Brivo CT385 Series</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-17.8584</v>
+        <v>6.052</v>
       </c>
       <c r="C15" t="n">
-        <v>-38.3008</v>
+        <v>-22.7964</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5839</v>
+        <v>34.9004</v>
       </c>
       <c r="E15" t="n">
-        <v>10.4222</v>
+        <v>14.708</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.7135</v>
+        <v>0.4115</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>8.6812e-02</t>
+          <t>6.8078e-01</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Model_Brivo CT385 Series</t>
+          <t>Model_Discovery CT750 HD</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6.3392</v>
+        <v>6.4249</v>
       </c>
       <c r="C16" t="n">
-        <v>-22.5116</v>
+        <v>-18.5699</v>
       </c>
       <c r="D16" t="n">
-        <v>35.19</v>
+        <v>31.4198</v>
       </c>
       <c r="E16" t="n">
-        <v>14.7092</v>
+        <v>12.7433</v>
       </c>
       <c r="F16" t="n">
-        <v>0.431</v>
+        <v>0.5042</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>6.6655e-01</t>
+          <t>6.1420e-01</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Model_Discovery CT750 HD</t>
+          <t>Model_Emotion 16</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>6.6202</v>
+        <v>-4.9247</v>
       </c>
       <c r="C17" t="n">
-        <v>-18.3752</v>
+        <v>-43.213</v>
       </c>
       <c r="D17" t="n">
-        <v>31.6157</v>
+        <v>33.3635</v>
       </c>
       <c r="E17" t="n">
-        <v>12.7436</v>
+        <v>19.5207</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5195</v>
+        <v>-0.2523</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>6.0348e-01</t>
+          <t>8.0085e-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Model_Emotion 16</t>
+          <t>Model_Emotion 6</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-4.4032</v>
+        <v>23.3289</v>
       </c>
       <c r="C18" t="n">
-        <v>-42.6997</v>
+        <v>-1.7179</v>
       </c>
       <c r="D18" t="n">
-        <v>33.8933</v>
+        <v>48.3757</v>
       </c>
       <c r="E18" t="n">
-        <v>19.5249</v>
+        <v>12.7698</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.2255</v>
+        <v>1.8269</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>8.2161e-01</t>
+          <t>6.7899e-02</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Model_Emotion 6</t>
+          <t>Model_IQon - Spectral CT</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>23.4444</v>
+        <v>-1.804</v>
       </c>
       <c r="C19" t="n">
-        <v>-1.6014</v>
+        <v>-26.8129</v>
       </c>
       <c r="D19" t="n">
-        <v>48.4903</v>
+        <v>23.205</v>
       </c>
       <c r="E19" t="n">
-        <v>12.7693</v>
+        <v>12.7504</v>
       </c>
       <c r="F19" t="n">
-        <v>1.836</v>
+        <v>-0.1415</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>6.6539e-02</t>
+          <t>8.8751e-01</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Model_IQon - Spectral CT</t>
+          <t>Model_Ingenuity CT</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-1.8151</v>
+        <v>25.9066</v>
       </c>
       <c r="C20" t="n">
-        <v>-26.8222</v>
+        <v>4.4163</v>
       </c>
       <c r="D20" t="n">
-        <v>23.192</v>
+        <v>47.397</v>
       </c>
       <c r="E20" t="n">
-        <v>12.7495</v>
+        <v>10.9566</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1424</v>
+        <v>2.3645</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>8.8681e-01</t>
+          <t>1.8171e-02</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Model_Ingenuity CT</t>
+          <t>Model_Ingenuity Core 128</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>25.6654</v>
+        <v>5.5976</v>
       </c>
       <c r="C21" t="n">
-        <v>4.1724</v>
+        <v>-9.5525</v>
       </c>
       <c r="D21" t="n">
-        <v>47.1584</v>
+        <v>20.7477</v>
       </c>
       <c r="E21" t="n">
-        <v>10.9579</v>
+        <v>7.724</v>
       </c>
       <c r="F21" t="n">
-        <v>2.3422</v>
+        <v>0.7247</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1.9291e-02</t>
+          <t>4.6874e-01</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Model_Ingenuity Core 128</t>
+          <t>Model_LightSpeed VCT</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>5.8293</v>
+        <v>2.7372</v>
       </c>
       <c r="C22" t="n">
-        <v>-9.325100000000001</v>
+        <v>-16.4057</v>
       </c>
       <c r="D22" t="n">
-        <v>20.9838</v>
+        <v>21.8801</v>
       </c>
       <c r="E22" t="n">
-        <v>7.7263</v>
+        <v>9.7597</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7544999999999999</v>
+        <v>0.2805</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>4.5067e-01</t>
+          <t>7.7916e-01</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Model_LightSpeed VCT</t>
+          <t>Model_LightSpeed16</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3.0077</v>
+        <v>34.4769</v>
       </c>
       <c r="C23" t="n">
-        <v>-16.1397</v>
+        <v>-3.7176</v>
       </c>
       <c r="D23" t="n">
-        <v>22.1552</v>
+        <v>72.6713</v>
       </c>
       <c r="E23" t="n">
-        <v>9.7621</v>
+        <v>19.4729</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3081</v>
+        <v>1.7705</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>7.5804e-01</t>
+          <t>7.6829e-02</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Model_LightSpeed16</t>
+          <t>Model_Optima CT660</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>33.998</v>
+        <v>-9.397</v>
       </c>
       <c r="C24" t="n">
-        <v>-4.203</v>
+        <v>-38.2515</v>
       </c>
       <c r="D24" t="n">
-        <v>72.199</v>
+        <v>19.4574</v>
       </c>
       <c r="E24" t="n">
-        <v>19.4762</v>
+        <v>14.711</v>
       </c>
       <c r="F24" t="n">
-        <v>1.7456</v>
+        <v>-0.6388</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>8.1066e-02</t>
+          <t>5.2306e-01</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Model_Optima CT660</t>
+          <t>Model_Revolution CT</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-8.820399999999999</v>
+        <v>1.3973</v>
       </c>
       <c r="C25" t="n">
-        <v>-37.6907</v>
+        <v>-13.7593</v>
       </c>
       <c r="D25" t="n">
-        <v>20.0499</v>
+        <v>16.554</v>
       </c>
       <c r="E25" t="n">
-        <v>14.7191</v>
+        <v>7.7274</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.5992</v>
+        <v>0.1808</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>5.4909e-01</t>
+          <t>8.5652e-01</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Model_Revolution CT</t>
+          <t>Model_Revolution EVO</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.5982</v>
+        <v>-31.9928</v>
       </c>
       <c r="C26" t="n">
-        <v>-13.5615</v>
+        <v>-70.1317</v>
       </c>
       <c r="D26" t="n">
-        <v>16.7579</v>
+        <v>6.1461</v>
       </c>
       <c r="E26" t="n">
-        <v>7.729</v>
+        <v>19.4446</v>
       </c>
       <c r="F26" t="n">
-        <v>0.2068</v>
+        <v>-1.6453</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>8.3620e-01</t>
+          <t>1.0009e-01</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Model_Revolution EVO</t>
+          <t>Model_SOMATOM Definition</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-32.0945</v>
+        <v>-11.2761</v>
       </c>
       <c r="C27" t="n">
-        <v>-70.2311</v>
+        <v>-40.9085</v>
       </c>
       <c r="D27" t="n">
-        <v>6.0421</v>
+        <v>18.3564</v>
       </c>
       <c r="E27" t="n">
-        <v>19.4434</v>
+        <v>15.1077</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.6507</v>
+        <v>-0.7464</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>9.9000e-02</t>
+          <t>4.5555e-01</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Definition</t>
+          <t>Model_SOMATOM Definition AS</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-11.6974</v>
+        <v>15.9474</v>
       </c>
       <c r="C28" t="n">
-        <v>-41.337</v>
+        <v>-3.829</v>
       </c>
       <c r="D28" t="n">
-        <v>17.9423</v>
+        <v>35.7238</v>
       </c>
       <c r="E28" t="n">
-        <v>15.1113</v>
+        <v>10.0827</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.7741</v>
+        <v>1.5817</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>4.3900e-01</t>
+          <t>1.1392e-01</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Definition AS</t>
+          <t>Model_SOMATOM Definition AS+</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>15.2494</v>
+        <v>1.2293</v>
       </c>
       <c r="C29" t="n">
-        <v>-4.5639</v>
+        <v>-13.8742</v>
       </c>
       <c r="D29" t="n">
-        <v>35.0626</v>
+        <v>16.3327</v>
       </c>
       <c r="E29" t="n">
-        <v>10.1015</v>
+        <v>7.7003</v>
       </c>
       <c r="F29" t="n">
-        <v>1.5096</v>
+        <v>0.1596</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1.3134e-01</t>
+          <t>8.7319e-01</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Definition AS+</t>
+          <t>Model_SOMATOM Definition Edge</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.3756</v>
+        <v>10.5568</v>
       </c>
       <c r="C30" t="n">
-        <v>-13.7289</v>
+        <v>-10.4097</v>
       </c>
       <c r="D30" t="n">
-        <v>16.4801</v>
+        <v>31.5232</v>
       </c>
       <c r="E30" t="n">
-        <v>7.7008</v>
+        <v>10.6895</v>
       </c>
       <c r="F30" t="n">
-        <v>0.1786</v>
+        <v>0.9876</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>8.5825e-01</t>
+          <t>3.2350e-01</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Definition Edge</t>
+          <t>Model_SOMATOM Definition Flash</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>10.1167</v>
+        <v>4.2226</v>
       </c>
       <c r="C31" t="n">
-        <v>-10.8626</v>
+        <v>-12.9661</v>
       </c>
       <c r="D31" t="n">
-        <v>31.0961</v>
+        <v>21.4113</v>
       </c>
       <c r="E31" t="n">
-        <v>10.696</v>
+        <v>8.763400000000001</v>
       </c>
       <c r="F31" t="n">
-        <v>0.9458</v>
+        <v>0.4818</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>3.4437e-01</t>
+          <t>6.2998e-01</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Definition Flash</t>
+          <t>Model_SOMATOM Drive</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4.2057</v>
+        <v>4.9247</v>
       </c>
       <c r="C32" t="n">
-        <v>-12.9818</v>
+        <v>-20.5993</v>
       </c>
       <c r="D32" t="n">
-        <v>21.3931</v>
+        <v>30.4487</v>
       </c>
       <c r="E32" t="n">
-        <v>8.7628</v>
+        <v>13.013</v>
       </c>
       <c r="F32" t="n">
-        <v>0.4799</v>
+        <v>0.3784</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>6.3133e-01</t>
+          <t>7.0515e-01</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Drive</t>
+          <t>Model_SOMATOM Force</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4.8634</v>
+        <v>13.0985</v>
       </c>
       <c r="C33" t="n">
-        <v>-20.659</v>
+        <v>-16.2381</v>
       </c>
       <c r="D33" t="n">
-        <v>30.3858</v>
+        <v>42.435</v>
       </c>
       <c r="E33" t="n">
-        <v>13.0122</v>
+        <v>14.9568</v>
       </c>
       <c r="F33" t="n">
-        <v>0.3738</v>
+        <v>0.8758</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>7.0863e-01</t>
+          <t>3.8129e-01</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Force</t>
+          <t>Model_SOMATOM Perspective</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>12.9745</v>
+        <v>5.0435</v>
       </c>
       <c r="C34" t="n">
-        <v>-16.3607</v>
+        <v>-33.1734</v>
       </c>
       <c r="D34" t="n">
-        <v>42.3097</v>
+        <v>43.2603</v>
       </c>
       <c r="E34" t="n">
-        <v>14.9561</v>
+        <v>19.4843</v>
       </c>
       <c r="F34" t="n">
-        <v>0.8675</v>
+        <v>0.2588</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>3.8579e-01</t>
+          <t>7.9579e-01</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Perspective</t>
+          <t>Model_Scope</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4.8646</v>
+        <v>21.3921</v>
       </c>
       <c r="C35" t="n">
-        <v>-33.3509</v>
+        <v>-16.8128</v>
       </c>
       <c r="D35" t="n">
-        <v>43.08</v>
+        <v>59.597</v>
       </c>
       <c r="E35" t="n">
-        <v>19.4836</v>
+        <v>19.4782</v>
       </c>
       <c r="F35" t="n">
-        <v>0.2497</v>
+        <v>1.0983</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>8.0287e-01</t>
+          <t>2.7225e-01</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Model_Scope</t>
+          <t>Model_Sensation 16</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>21.1149</v>
+        <v>43.2649</v>
       </c>
       <c r="C36" t="n">
-        <v>-17.0904</v>
+        <v>14.4029</v>
       </c>
       <c r="D36" t="n">
-        <v>59.3202</v>
+        <v>72.127</v>
       </c>
       <c r="E36" t="n">
-        <v>19.4784</v>
+        <v>14.7149</v>
       </c>
       <c r="F36" t="n">
-        <v>1.084</v>
+        <v>2.9402</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2.7852e-01</t>
+          <t>3.3260e-03</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Model_Sensation 16</t>
+          <t>Model_Sensation 64</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>43.3607</v>
+        <v>-1.2798</v>
       </c>
       <c r="C37" t="n">
-        <v>14.5003</v>
+        <v>-16.3671</v>
       </c>
       <c r="D37" t="n">
-        <v>72.2212</v>
+        <v>13.8075</v>
       </c>
       <c r="E37" t="n">
-        <v>14.7141</v>
+        <v>7.6921</v>
       </c>
       <c r="F37" t="n">
-        <v>2.9469</v>
+        <v>-0.1664</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>3.2554e-03</t>
+          <t>8.6788e-01</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Model_Sensation 64</t>
+          <t>Model_iCT 128</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.2626</v>
+        <v>-49.013</v>
       </c>
       <c r="C38" t="n">
-        <v>-16.3489</v>
+        <v>-87.2508</v>
       </c>
       <c r="D38" t="n">
-        <v>13.8237</v>
+        <v>-10.7752</v>
       </c>
       <c r="E38" t="n">
-        <v>7.6915</v>
+        <v>19.495</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.1642</v>
+        <v>-2.5141</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>8.6963e-01</t>
+          <t>1.2028e-02</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Model_iCT 128</t>
+          <t>Model_iCT 256</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-48.6497</v>
+        <v>22.4044</v>
       </c>
       <c r="C39" t="n">
-        <v>-86.89019999999999</v>
+        <v>2.6147</v>
       </c>
       <c r="D39" t="n">
-        <v>-10.4093</v>
+        <v>42.194</v>
       </c>
       <c r="E39" t="n">
-        <v>19.4963</v>
+        <v>10.0895</v>
       </c>
       <c r="F39" t="n">
-        <v>-2.4953</v>
+        <v>2.2206</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>1.2682e-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Model_iCT 256</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>22.5784</v>
-      </c>
-      <c r="C40" t="n">
-        <v>2.7878</v>
-      </c>
-      <c r="D40" t="n">
-        <v>42.369</v>
-      </c>
-      <c r="E40" t="n">
-        <v>10.09</v>
-      </c>
-      <c r="F40" t="n">
-        <v>2.2377</v>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>2.5374e-02</t>
+          <t>2.6517e-02</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2848,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:H39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2984,26 +2900,26 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.9401</v>
+        <v>-0.9513</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3906</v>
+        <v>0.3862</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0605</v>
+        <v>0.0592</v>
       </c>
       <c r="E2" t="n">
-        <v>2.5227</v>
+        <v>2.5194</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9518</v>
+        <v>0.9568</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.9877</v>
+        <v>-0.9942</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3.2329e-01</t>
+          <t>3.2010e-01</t>
         </is>
       </c>
     </row>
@@ -3014,26 +2930,26 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1662</v>
+        <v>0.1442</v>
       </c>
       <c r="C3" t="n">
-        <v>1.1809</v>
+        <v>1.1552</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8815</v>
+        <v>0.8648</v>
       </c>
       <c r="E3" t="n">
-        <v>1.5819</v>
+        <v>1.5431</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1492</v>
+        <v>0.1477</v>
       </c>
       <c r="G3" t="n">
-        <v>1.1143</v>
+        <v>0.9762999999999999</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2.6515e-01</t>
+          <t>3.2890e-01</t>
         </is>
       </c>
     </row>
@@ -3044,56 +2960,56 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6088</v>
+        <v>0.6072</v>
       </c>
       <c r="C4" t="n">
-        <v>1.8382</v>
+        <v>1.8352</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5895</v>
+        <v>1.5865</v>
       </c>
       <c r="E4" t="n">
-        <v>2.126</v>
+        <v>2.1229</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0742</v>
+        <v>0.0743</v>
       </c>
       <c r="G4" t="n">
-        <v>8.2056</v>
+        <v>8.1724</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2.2953e-16</t>
+          <t>3.0237e-16</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>p25_z</t>
+          <t>mean_z</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.6647999999999999</v>
+        <v>-0.9767</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5144</v>
+        <v>0.3766</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1697</v>
+        <v>0.3082</v>
       </c>
       <c r="E5" t="n">
-        <v>1.5588</v>
+        <v>0.4601</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5657</v>
+        <v>0.1023</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.1752</v>
+        <v>-9.551399999999999</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2.3990e-01</t>
+          <t>1.2798e-21</t>
         </is>
       </c>
     </row>
@@ -3104,26 +3020,26 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.0181</v>
+        <v>0.08690000000000001</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9821</v>
+        <v>1.0908</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7722</v>
+        <v>0.9256</v>
       </c>
       <c r="E6" t="n">
-        <v>1.2491</v>
+        <v>1.2855</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1227</v>
+        <v>0.0838</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.1471</v>
+        <v>1.0372</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>8.8304e-01</t>
+          <t>2.9965e-01</t>
         </is>
       </c>
     </row>
@@ -3134,26 +3050,26 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.1364</v>
       </c>
       <c r="C7" t="n">
-        <v>1.074</v>
+        <v>1.1461</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8853</v>
+        <v>0.977</v>
       </c>
       <c r="E7" t="n">
-        <v>1.3029</v>
+        <v>1.3446</v>
       </c>
       <c r="F7" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.0815</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7244</v>
+        <v>1.6742</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>4.6881e-01</t>
+          <t>9.4098e-02</t>
         </is>
       </c>
     </row>
@@ -3164,950 +3080,954 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2482</v>
+        <v>0.2654</v>
       </c>
       <c r="C8" t="n">
-        <v>1.2817</v>
+        <v>1.3039</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0434</v>
+        <v>1.0655</v>
       </c>
       <c r="E8" t="n">
-        <v>1.5744</v>
+        <v>1.5958</v>
       </c>
       <c r="F8" t="n">
-        <v>0.105</v>
+        <v>0.103</v>
       </c>
       <c r="G8" t="n">
-        <v>2.3645</v>
+        <v>2.5755</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.8053e-02</t>
+          <t>1.0009e-02</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>mean_z</t>
+          <t>kvp_z</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.3931</v>
+        <v>-0.1486</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6749000000000001</v>
+        <v>0.8619</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2506</v>
+        <v>0.7274</v>
       </c>
       <c r="E9" t="n">
-        <v>1.8179</v>
+        <v>1.0214</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5054999999999999</v>
+        <v>0.0866</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.7776</v>
+        <v>-1.7159</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>4.3678e-01</t>
+          <t>8.6175e-02</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>kvp_z</t>
+          <t>Model_Aquilion ONE</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.1515</v>
+        <v>-6.2815</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8594000000000001</v>
+        <v>0.0019</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7249</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>1.019</v>
+        <v>6.220440227080598e+20</v>
       </c>
       <c r="F10" t="n">
-        <v>0.08690000000000001</v>
+        <v>27.6337</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.7437</v>
+        <v>-0.2273</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>8.1204e-02</t>
+          <t>8.2018e-01</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Model_Aquilion ONE</t>
+          <t>Model_Aquilion PRIME</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-6.3156</v>
+        <v>-0.7299</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0018</v>
+        <v>0.4819</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>0.0277</v>
       </c>
       <c r="E11" t="n">
-        <v>4.587746468011121e+19</v>
+        <v>8.3744</v>
       </c>
       <c r="F11" t="n">
-        <v>26.3209</v>
+        <v>1.4567</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.2399</v>
+        <v>-0.5011</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>8.1037e-01</t>
+          <t>6.1632e-01</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Model_Aquilion PRIME</t>
+          <t>Model_BrightSpeed</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.7612</v>
+        <v>-9.426399999999999</v>
       </c>
       <c r="C12" t="n">
-        <v>0.4671</v>
+        <v>0.0001</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0269</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>8.1214</v>
+        <v>6.220813682302936e+68</v>
       </c>
       <c r="F12" t="n">
-        <v>1.457</v>
+        <v>85.6292</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.5225</v>
+        <v>-0.1101</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6.0135e-01</t>
+          <t>9.1234e-01</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Model_BrightSpeed</t>
+          <t>Model_BrightSpeed S</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-8.6256</v>
+        <v>-0.3868</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0002</v>
+        <v>0.6792</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>5.345630565580465e+46</v>
+        <v>112196986.2855</v>
       </c>
       <c r="F13" t="n">
-        <v>59.2974</v>
+        <v>9.654500000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.1455</v>
+        <v>-0.0401</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>8.8435e-01</t>
+          <t>9.6804e-01</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Model_BrightSpeed S</t>
+          <t>Model_Brilliance 64</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.434</v>
+        <v>0.2167</v>
       </c>
       <c r="C14" t="n">
-        <v>0.6479</v>
+        <v>1.2419</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>0.0916</v>
       </c>
       <c r="E14" t="n">
-        <v>45540262.9773</v>
+        <v>16.8432</v>
       </c>
       <c r="F14" t="n">
-        <v>9.2186</v>
+        <v>1.3303</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.0471</v>
+        <v>0.1629</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>9.6245e-01</t>
+          <t>8.7062e-01</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Model_Brilliance 64</t>
+          <t>Model_Brivo CT385 Series</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1828</v>
+        <v>-0.0648</v>
       </c>
       <c r="C15" t="n">
-        <v>1.2006</v>
+        <v>0.9373</v>
       </c>
       <c r="D15" t="n">
-        <v>0.089</v>
+        <v>0.0303</v>
       </c>
       <c r="E15" t="n">
-        <v>16.1908</v>
+        <v>28.9519</v>
       </c>
       <c r="F15" t="n">
-        <v>1.3274</v>
+        <v>1.7502</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1377</v>
+        <v>-0.037</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>8.9045e-01</t>
+          <t>9.7047e-01</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Model_Brivo CT385 Series</t>
+          <t>Model_Discovery CT750 HD</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.1259</v>
+        <v>-6.6445</v>
       </c>
       <c r="C16" t="n">
-        <v>0.8817</v>
+        <v>0.0013</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0285</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>27.3196</v>
+        <v>6.590840500483285e+25</v>
       </c>
       <c r="F16" t="n">
-        <v>1.7518</v>
+        <v>33.7225</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.07190000000000001</v>
+        <v>-0.197</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>9.4270e-01</t>
+          <t>8.4380e-01</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Model_Discovery CT750 HD</t>
+          <t>Model_Emotion 16</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-6.3146</v>
+        <v>-9.640499999999999</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0018</v>
+        <v>0.0001</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>2.426225546661863e+21</v>
+        <v>1.392008468729414e+76</v>
       </c>
       <c r="F17" t="n">
-        <v>28.345</v>
+        <v>94.373</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.2228</v>
+        <v>-0.1022</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>8.2371e-01</t>
+          <t>9.1863e-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Model_Emotion 16</t>
+          <t>Model_Emotion 6</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-9.3443</v>
+        <v>-14.9934</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
-      <c r="E18" t="n">
-        <v>3.890318194116966e+62</v>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
       <c r="F18" t="n">
-        <v>78.2989</v>
+        <v>824.2898</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.1193</v>
+        <v>-0.0182</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>9.0500e-01</t>
+          <t>9.8549e-01</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Model_Emotion 6</t>
+          <t>Model_IQon - Spectral CT</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-14.2615</v>
+        <v>-0.5874</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>0.5558</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>0.0236</v>
+      </c>
+      <c r="E19" t="n">
+        <v>13.0674</v>
       </c>
       <c r="F19" t="n">
-        <v>560.2224</v>
+        <v>1.611</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.0255</v>
+        <v>-0.3646</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>9.7969e-01</t>
+          <t>7.1539e-01</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Model_IQon - Spectral CT</t>
+          <t>Model_Ingenuity CT</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.6155</v>
+        <v>-16.6904</v>
       </c>
       <c r="C20" t="n">
-        <v>0.5404</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0228</v>
-      </c>
-      <c r="E20" t="n">
-        <v>12.8126</v>
+        <v>0</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
       <c r="F20" t="n">
-        <v>1.6153</v>
+        <v>1744.3734</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.381</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>7.0317e-01</t>
+          <t>9.9237e-01</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Model_Ingenuity CT</t>
+          <t>Model_Ingenuity Core 128</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-15.5522</v>
+        <v>-0.7756999999999999</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>0.4604</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>0.06859999999999999</v>
+      </c>
+      <c r="E21" t="n">
+        <v>3.0902</v>
       </c>
       <c r="F21" t="n">
-        <v>991.097</v>
+        <v>0.9714</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.0157</v>
+        <v>-0.7985</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>9.8748e-01</t>
+          <t>4.2456e-01</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Model_Ingenuity Core 128</t>
+          <t>Model_LightSpeed VCT</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.8124</v>
+        <v>-1.2289</v>
       </c>
       <c r="C22" t="n">
-        <v>0.4438</v>
+        <v>0.2926</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0667</v>
+        <v>0.0238</v>
       </c>
       <c r="E22" t="n">
-        <v>2.9527</v>
+        <v>3.593</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9669</v>
+        <v>1.2795</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.8401999999999999</v>
+        <v>-0.9604</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>4.0080e-01</t>
+          <t>3.3685e-01</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Model_LightSpeed VCT</t>
+          <t>Model_LightSpeed16</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-1.2673</v>
+        <v>-11.2487</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2816</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0231</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>3.4313</v>
+        <v>6.152157656371505e+137</v>
       </c>
       <c r="F23" t="n">
-        <v>1.2756</v>
+        <v>167.6152</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.9933999999999999</v>
+        <v>-0.06710000000000001</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>3.2049e-01</t>
+          <t>9.4649e-01</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Model_LightSpeed16</t>
+          <t>Model_Optima CT660</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-10.3424</v>
+        <v>19.845</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>415512651.062</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
-      <c r="E24" t="n">
-        <v>1.013251935235954e+89</v>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
       <c r="F24" t="n">
-        <v>109.8416</v>
+        <v>17641.4614</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.09420000000000001</v>
+        <v>0.0011</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>9.2498e-01</t>
+          <t>9.9910e-01</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Model_Optima CT660</t>
+          <t>Model_Revolution CT</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>18.1414</v>
+        <v>-0.8641</v>
       </c>
       <c r="C25" t="n">
-        <v>75631977.9851</v>
+        <v>0.4214</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>0.06270000000000001</v>
+      </c>
+      <c r="E25" t="n">
+        <v>2.8312</v>
       </c>
       <c r="F25" t="n">
-        <v>7766.0448</v>
+        <v>0.9719</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0023</v>
+        <v>-0.8891</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>9.9814e-01</t>
+          <t>3.7394e-01</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Model_Revolution CT</t>
+          <t>Model_Revolution EVO</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.902</v>
+        <v>14.3842</v>
       </c>
       <c r="C26" t="n">
-        <v>0.4057</v>
+        <v>1765984.7918</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0609</v>
-      </c>
-      <c r="E26" t="n">
-        <v>2.703</v>
+        <v>0</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
       <c r="F26" t="n">
-        <v>0.9676</v>
+        <v>1893.6045</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.9323</v>
+        <v>0.0076</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>3.5120e-01</t>
+          <t>9.9394e-01</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Model_Revolution EVO</t>
+          <t>Model_SOMATOM Definition</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>13.4815</v>
+        <v>1.1907</v>
       </c>
       <c r="C27" t="n">
-        <v>716040.6875</v>
+        <v>3.2893</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>0.1014</v>
+      </c>
+      <c r="E27" t="n">
+        <v>106.65</v>
       </c>
       <c r="F27" t="n">
-        <v>1199.4315</v>
+        <v>1.775</v>
       </c>
       <c r="G27" t="n">
-        <v>0.0112</v>
+        <v>0.6708</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>9.9103e-01</t>
+          <t>5.0234e-01</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Definition</t>
+          <t>Model_SOMATOM Definition AS</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.2601</v>
+        <v>-22.4052</v>
       </c>
       <c r="C28" t="n">
-        <v>3.5258</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1051</v>
-      </c>
-      <c r="E28" t="n">
-        <v>118.231</v>
+        <v>0</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
       <c r="F28" t="n">
-        <v>1.7921</v>
+        <v>23792.4986</v>
       </c>
       <c r="G28" t="n">
-        <v>0.7030999999999999</v>
+        <v>-0.0009</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>4.8198e-01</t>
+          <t>9.9925e-01</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Definition AS</t>
+          <t>Model_SOMATOM Definition AS+</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-19.9528</v>
+        <v>-0.4262</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>0.653</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>0.0983</v>
+      </c>
+      <c r="E29" t="n">
+        <v>4.3386</v>
       </c>
       <c r="F29" t="n">
-        <v>7463.2107</v>
+        <v>0.9661999999999999</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.0027</v>
+        <v>-0.4411</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>9.9787e-01</t>
+          <t>6.5912e-01</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Definition AS+</t>
+          <t>Model_SOMATOM Definition Edge</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.4531</v>
+        <v>-0.4202</v>
       </c>
       <c r="C30" t="n">
-        <v>0.6357</v>
+        <v>0.6569</v>
       </c>
       <c r="D30" t="n">
-        <v>0.09660000000000001</v>
+        <v>0.042</v>
       </c>
       <c r="E30" t="n">
-        <v>4.1837</v>
+        <v>10.2786</v>
       </c>
       <c r="F30" t="n">
-        <v>0.9614</v>
+        <v>1.4032</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.4713</v>
+        <v>-0.2994</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>6.3745e-01</t>
+          <t>7.6460e-01</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Definition Edge</t>
+          <t>Model_SOMATOM Definition Flash</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.3496</v>
+        <v>-1.0103</v>
       </c>
       <c r="C31" t="n">
-        <v>0.7049</v>
+        <v>0.3641</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0451</v>
+        <v>0.0384</v>
       </c>
       <c r="E31" t="n">
-        <v>11.0244</v>
+        <v>3.456</v>
       </c>
       <c r="F31" t="n">
-        <v>1.403</v>
+        <v>1.1482</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.2492</v>
+        <v>-0.8799</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>8.0319e-01</t>
+          <t>3.7891e-01</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Definition Flash</t>
+          <t>Model_SOMATOM Drive</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-1.0127</v>
+        <v>-0.9416</v>
       </c>
       <c r="C32" t="n">
-        <v>0.3632</v>
+        <v>0.39</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0386</v>
+        <v>0.0177</v>
       </c>
       <c r="E32" t="n">
-        <v>3.4193</v>
+        <v>8.580500000000001</v>
       </c>
       <c r="F32" t="n">
-        <v>1.144</v>
+        <v>1.5771</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.8853</v>
+        <v>-0.597</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>3.7601e-01</t>
+          <t>5.5049e-01</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Drive</t>
+          <t>Model_SOMATOM Force</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.9283</v>
+        <v>-13.5394</v>
       </c>
       <c r="C33" t="n">
-        <v>0.3952</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0181</v>
-      </c>
-      <c r="E33" t="n">
-        <v>8.650399999999999</v>
+        <v>0</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
       <c r="F33" t="n">
-        <v>1.5745</v>
+        <v>415.484</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.5896</v>
+        <v>-0.0326</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>5.5546e-01</t>
+          <t>9.7400e-01</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Force</t>
+          <t>Model_SOMATOM Perspective</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-12.6807</v>
+        <v>-9.3878</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>5.741470016050721e+224</v>
+        <v>6.081837155634923e+69</v>
       </c>
       <c r="F34" t="n">
-        <v>270.519</v>
+        <v>86.7727</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.0469</v>
+        <v>-0.1082</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>9.6261e-01</t>
+          <t>9.1385e-01</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Perspective</t>
+          <t>Model_Scope</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-8.744899999999999</v>
+        <v>-6.6813</v>
       </c>
       <c r="C35" t="n">
-        <v>0.0002</v>
+        <v>0.0013</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>2.206041216134128e+50</v>
+        <v>1.420889233468816e+25</v>
       </c>
       <c r="F35" t="n">
-        <v>63.6059</v>
+        <v>32.9584</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.1375</v>
+        <v>-0.2027</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>8.9065e-01</t>
+          <t>8.3935e-01</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Model_Scope</t>
+          <t>Model_Sensation 16</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-6.1847</v>
+        <v>-10.8502</v>
       </c>
       <c r="C36" t="n">
-        <v>0.0021</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>3.850303718821931e+19</v>
+        <v>1.096857403880161e+124</v>
       </c>
       <c r="F36" t="n">
-        <v>26.1647</v>
+        <v>151.2595</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.2364</v>
+        <v>-0.0717</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>8.1314e-01</t>
+          <t>9.4281e-01</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Model_Sensation 16</t>
+          <t>Model_Sensation 64</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-10.1312</v>
+        <v>-0.1038</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>0.9014</v>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>0.1357</v>
       </c>
       <c r="E37" t="n">
-        <v>2.840108154452759e+86</v>
+        <v>5.9897</v>
       </c>
       <c r="F37" t="n">
-        <v>106.7353</v>
+        <v>0.9663</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.0949</v>
+        <v>-0.1074</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>9.2438e-01</t>
+          <t>9.1446e-01</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Model_Sensation 64</t>
+          <t>Model_iCT 128</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.112</v>
+        <v>29.824</v>
       </c>
       <c r="C38" t="n">
-        <v>0.8941</v>
+        <v>8961912282508.865</v>
       </c>
       <c r="D38" t="n">
-        <v>0.1359</v>
-      </c>
-      <c r="E38" t="n">
-        <v>5.8823</v>
+        <v>0</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
       <c r="F38" t="n">
-        <v>0.9612000000000001</v>
+        <v>617839.5298</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.1165</v>
+        <v>0</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>9.0726e-01</t>
+          <t>9.9996e-01</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Model_iCT 128</t>
+          <t>Model_iCT 256</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>27.5745</v>
+        <v>-18.8937</v>
       </c>
       <c r="C39" t="n">
-        <v>945015421155.9644</v>
+        <v>0</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
@@ -4118,46 +4038,14 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>206110.5988</v>
+        <v>5216.885</v>
       </c>
       <c r="G39" t="n">
-        <v>0.0001</v>
+        <v>-0.0036</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>9.9989e-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Model_iCT 256</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>-17.8619</v>
-      </c>
-      <c r="C40" t="n">
-        <v>0</v>
-      </c>
-      <c r="D40" t="n">
-        <v>0</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-      <c r="F40" t="n">
-        <v>3060.6091</v>
-      </c>
-      <c r="G40" t="n">
-        <v>-0.0058</v>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>9.9534e-01</t>
+          <t>9.9711e-01</t>
         </is>
       </c>
     </row>
@@ -4204,7 +4092,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6599</v>
+        <v>0.6597</v>
       </c>
     </row>
     <row r="4">
@@ -4224,7 +4112,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>83.44580000000001</v>
+        <v>85.6553</v>
       </c>
     </row>
     <row r="6">
@@ -4246,7 +4134,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17.7773</v>
+        <v>17.784</v>
       </c>
     </row>
     <row r="8">
@@ -4256,7 +4144,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13.1377</v>
+        <v>13.1539</v>
       </c>
     </row>
     <row r="9">
@@ -4266,7 +4154,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14455.29</v>
+        <v>14454.56</v>
       </c>
     </row>
     <row r="10">
@@ -4276,7 +4164,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14666.77</v>
+        <v>14660.61</v>
       </c>
     </row>
   </sheetData>
@@ -4332,7 +4220,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7548</v>
+        <v>0.7542</v>
       </c>
     </row>
     <row r="5">
@@ -4342,7 +4230,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7297</v>
+        <v>0.7289</v>
       </c>
     </row>
     <row r="6">
@@ -4352,7 +4240,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7806</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="7">
@@ -4362,7 +4250,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.3981</v>
+        <v>5.2713</v>
       </c>
     </row>
     <row r="8">
@@ -4373,7 +4261,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4.9435e-01</t>
+          <t>7.2822e-01</t>
         </is>
       </c>
     </row>
@@ -4396,7 +4284,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.2169</v>
+        <v>0.2159</v>
       </c>
     </row>
     <row r="11">
@@ -4406,7 +4294,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1553</v>
+        <v>0.1554</v>
       </c>
     </row>
     <row r="12">
@@ -4416,7 +4304,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1656.88</v>
+        <v>1656.25</v>
       </c>
     </row>
     <row r="13">
@@ -4426,7 +4314,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1868.35</v>
+        <v>1862.3</v>
       </c>
     </row>
     <row r="14">
@@ -4450,7 +4338,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4500,16 +4388,16 @@
         <v>122.5105</v>
       </c>
       <c r="C2" t="n">
-        <v>121.1955</v>
+        <v>121.1935</v>
       </c>
       <c r="D2" t="n">
-        <v>123.8254</v>
+        <v>123.8274</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6704</v>
+        <v>0.6714</v>
       </c>
       <c r="F2" t="n">
-        <v>182.7412</v>
+        <v>182.4647</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -4520,27 +4408,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>p25_z</t>
+          <t>mean_z</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13.964</v>
+        <v>5.6945</v>
       </c>
       <c r="C3" t="n">
-        <v>2.8375</v>
+        <v>4.0903</v>
       </c>
       <c r="D3" t="n">
-        <v>25.0906</v>
+        <v>7.2987</v>
       </c>
       <c r="E3" t="n">
-        <v>5.6728</v>
+        <v>0.8179</v>
       </c>
       <c r="F3" t="n">
-        <v>2.4616</v>
+        <v>6.9622</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1.3933e-02</t>
+          <t>4.7987e-12</t>
         </is>
       </c>
     </row>
@@ -4551,23 +4439,23 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-4.0635</v>
+        <v>-6.4456</v>
       </c>
       <c r="C4" t="n">
-        <v>-6.5089</v>
+        <v>-7.9898</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.618</v>
+        <v>-4.9014</v>
       </c>
       <c r="E4" t="n">
-        <v>1.2468</v>
+        <v>0.7873</v>
       </c>
       <c r="F4" t="n">
-        <v>-3.2592</v>
+        <v>-8.1869</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1.1399e-03</t>
+          <t>5.2643e-16</t>
         </is>
       </c>
     </row>
@@ -4578,23 +4466,23 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-4.0437</v>
+        <v>-5.618</v>
       </c>
       <c r="C5" t="n">
-        <v>-6.0322</v>
+        <v>-7.1633</v>
       </c>
       <c r="D5" t="n">
-        <v>-2.0552</v>
+        <v>-4.0728</v>
       </c>
       <c r="E5" t="n">
-        <v>1.0138</v>
+        <v>0.7877999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>-3.9886</v>
+        <v>-7.131</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>6.9348e-05</t>
+          <t>1.4791e-12</t>
         </is>
       </c>
     </row>
@@ -4605,50 +4493,23 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.9684</v>
+        <v>-1.199</v>
       </c>
       <c r="C6" t="n">
-        <v>-2.4966</v>
+        <v>-2.7184</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5598</v>
+        <v>0.3204</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7791</v>
+        <v>0.7747000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.2429</v>
+        <v>-1.5478</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2.1406e-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>mean_z</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>-6.654</v>
-      </c>
-      <c r="C7" t="n">
-        <v>-16.6228</v>
-      </c>
-      <c r="D7" t="n">
-        <v>3.3148</v>
-      </c>
-      <c r="E7" t="n">
-        <v>5.0825</v>
-      </c>
-      <c r="F7" t="n">
-        <v>-1.3092</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>1.9065e-01</t>
+          <t>1.2186e-01</t>
         </is>
       </c>
     </row>
@@ -4663,7 +4524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4715,56 +4576,56 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-1.2663</v>
+        <v>-1.2649</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2819</v>
+        <v>0.2823</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2492</v>
+        <v>0.2496</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3188</v>
+        <v>0.3192</v>
       </c>
       <c r="F2" t="n">
-        <v>0.06279999999999999</v>
+        <v>0.06270000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>-20.1615</v>
+        <v>-20.1738</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2.1311e-90</t>
+          <t>1.6629e-90</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>p25_z</t>
+          <t>mean_z</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.3573</v>
+        <v>-0.7651</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6996</v>
+        <v>0.4653</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2506</v>
+        <v>0.3984</v>
       </c>
       <c r="E3" t="n">
-        <v>1.9529</v>
+        <v>0.5434</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5238</v>
+        <v>0.07920000000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.6821</v>
+        <v>-9.6561</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4.9516e-01</t>
+          <t>4.6332e-22</t>
         </is>
       </c>
     </row>
@@ -4775,26 +4636,26 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.1491</v>
+        <v>-0.0897</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8615</v>
+        <v>0.9142</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6944</v>
+        <v>0.802</v>
       </c>
       <c r="E4" t="n">
-        <v>1.0687</v>
+        <v>1.0421</v>
       </c>
       <c r="F4" t="n">
-        <v>0.11</v>
+        <v>0.0668</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.3558</v>
+        <v>-1.3433</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.7515e-01</t>
+          <t>1.7917e-01</t>
         </is>
       </c>
     </row>
@@ -4805,26 +4666,26 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.0291</v>
+        <v>0.0077</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9713000000000001</v>
+        <v>1.0077</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8147</v>
+        <v>0.8759</v>
       </c>
       <c r="E5" t="n">
-        <v>1.1581</v>
+        <v>1.1594</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0897</v>
+        <v>0.07149999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.3242</v>
+        <v>0.1078</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>7.4576e-01</t>
+          <t>9.1415e-01</t>
         </is>
       </c>
     </row>
@@ -4835,56 +4696,26 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3778</v>
+        <v>0.3825</v>
       </c>
       <c r="C6" t="n">
-        <v>1.4591</v>
+        <v>1.466</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2731</v>
+        <v>1.2803</v>
       </c>
       <c r="E6" t="n">
-        <v>1.6724</v>
+        <v>1.6787</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0696</v>
+        <v>0.06909999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>5.4285</v>
+        <v>5.535</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>5.6815e-08</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>mean_z</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>-0.4516</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0.6366000000000001</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.2555</v>
-      </c>
-      <c r="E7" t="n">
-        <v>1.5864</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.4658</v>
-      </c>
-      <c r="G7" t="n">
-        <v>-0.9694</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>3.3236e-01</t>
+          <t>3.1131e-08</t>
         </is>
       </c>
     </row>
@@ -4931,7 +4762,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1938</v>
+        <v>0.1909</v>
       </c>
     </row>
     <row r="4">
@@ -4941,7 +4772,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1914</v>
+        <v>0.1889</v>
       </c>
     </row>
     <row r="5">
@@ -4951,7 +4782,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>80.1455</v>
+        <v>98.3687</v>
       </c>
     </row>
     <row r="6">
@@ -4962,7 +4793,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.6316e-75</t>
+          <t>3.1021e-75</t>
         </is>
       </c>
     </row>
@@ -4973,7 +4804,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>27.3719</v>
+        <v>27.4216</v>
       </c>
     </row>
     <row r="8">
@@ -4983,7 +4814,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>21.5901</v>
+        <v>21.6665</v>
       </c>
     </row>
     <row r="9">
@@ -4993,7 +4824,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15833.41</v>
+        <v>15837.48</v>
       </c>
     </row>
     <row r="10">
@@ -5003,7 +4834,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>15865.94</v>
+        <v>15864.59</v>
       </c>
     </row>
   </sheetData>
@@ -5069,7 +4900,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6512</v>
+        <v>0.651</v>
       </c>
     </row>
     <row r="6">
@@ -5079,7 +4910,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7065</v>
+        <v>0.7064</v>
       </c>
     </row>
     <row r="7">
@@ -5089,7 +4920,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15.5536</v>
+        <v>12.4577</v>
       </c>
     </row>
     <row r="8">
@@ -5100,7 +4931,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4.9233e-02</t>
+          <t>1.3192e-01</t>
         </is>
       </c>
     </row>
@@ -5112,7 +4943,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>보정 불량</t>
+          <t>보정 양호</t>
         </is>
       </c>
     </row>
@@ -5123,7 +4954,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.0979</v>
+        <v>0.09760000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -5143,7 +4974,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1739.35</v>
+        <v>1737.82</v>
       </c>
     </row>
     <row r="13">
@@ -5153,7 +4984,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1771.88</v>
+        <v>1764.93</v>
       </c>
     </row>
     <row r="14">
